--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N66_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N66_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.76354353886522</v>
+        <v>4.024075825065599</v>
       </c>
       <c r="D2" t="n">
-        <v>24.61304267745357</v>
+        <v>3.999619435086206</v>
       </c>
       <c r="E2" t="n">
-        <v>7.98097201914586</v>
+        <v>1.296907953111202</v>
       </c>
       <c r="F2" t="n">
-        <v>7.986301554136606</v>
+        <v>1.297774002547199</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.46367620458937</v>
+        <v>3.650347383245772</v>
       </c>
       <c r="D3" t="n">
-        <v>22.57273332395535</v>
+        <v>3.668069165142745</v>
       </c>
       <c r="E3" t="n">
-        <v>7.98097201914586</v>
+        <v>1.296907953111202</v>
       </c>
       <c r="F3" t="n">
-        <v>7.986301554136606</v>
+        <v>1.297774002547199</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.02910526712707</v>
+        <v>5.367229605908149</v>
       </c>
       <c r="D4" t="n">
-        <v>33.14363278954473</v>
+        <v>5.385840328301019</v>
       </c>
       <c r="E4" t="n">
-        <v>7.98097201914586</v>
+        <v>1.296907953111202</v>
       </c>
       <c r="F4" t="n">
-        <v>7.986301554136606</v>
+        <v>1.297774002547199</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.56434587549044</v>
+        <v>5.129206204767197</v>
       </c>
       <c r="D5" t="n">
-        <v>31.55415520241548</v>
+        <v>5.127550220392516</v>
       </c>
       <c r="E5" t="n">
-        <v>7.98097201914586</v>
+        <v>1.296907953111202</v>
       </c>
       <c r="F5" t="n">
-        <v>7.986301554136606</v>
+        <v>1.297774002547199</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.54957249174183</v>
+        <v>3.664305529908048</v>
       </c>
       <c r="D6" t="n">
-        <v>22.74432515814386</v>
+        <v>3.695952838198377</v>
       </c>
       <c r="E6" t="n">
-        <v>7.98097201914586</v>
+        <v>1.296907953111202</v>
       </c>
       <c r="F6" t="n">
-        <v>7.986301554136606</v>
+        <v>1.297774002547199</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.88442991772347</v>
+        <v>4.043719861630064</v>
       </c>
       <c r="D7" t="n">
-        <v>24.68814883547017</v>
+        <v>4.011824185763903</v>
       </c>
       <c r="E7" t="n">
-        <v>7.98097201914586</v>
+        <v>1.296907953111202</v>
       </c>
       <c r="F7" t="n">
-        <v>7.986301554136606</v>
+        <v>1.297774002547199</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>14.78822704665354</v>
+        <v>2.403086895081199</v>
       </c>
       <c r="D8" t="n">
-        <v>14.83520750792671</v>
+        <v>2.410721220038091</v>
       </c>
       <c r="E8" t="n">
-        <v>7.98097201914586</v>
+        <v>1.296907953111202</v>
       </c>
       <c r="F8" t="n">
-        <v>7.986301554136606</v>
+        <v>1.297774002547199</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.43279268099816</v>
+        <v>4.945328810662201</v>
       </c>
       <c r="D9" t="n">
-        <v>30.53274822612116</v>
+        <v>4.961571586744689</v>
       </c>
       <c r="E9" t="n">
-        <v>7.98097201914586</v>
+        <v>1.296907953111202</v>
       </c>
       <c r="F9" t="n">
-        <v>7.986301554136606</v>
+        <v>1.297774002547199</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.47264742254953</v>
+        <v>4.626805206164298</v>
       </c>
       <c r="D10" t="n">
-        <v>28.50055759038984</v>
+        <v>4.631340608438349</v>
       </c>
       <c r="E10" t="n">
-        <v>7.98097201914586</v>
+        <v>1.296907953111202</v>
       </c>
       <c r="F10" t="n">
-        <v>7.986301554136606</v>
+        <v>1.297774002547199</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.28516861135065</v>
+        <v>5.246339899344481</v>
       </c>
       <c r="D11" t="n">
-        <v>32.28240817024093</v>
+        <v>5.245891327664152</v>
       </c>
       <c r="E11" t="n">
-        <v>7.98097201914586</v>
+        <v>1.296907953111202</v>
       </c>
       <c r="F11" t="n">
-        <v>7.986301554136606</v>
+        <v>1.297774002547199</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>27.02648456875545</v>
+        <v>4.39180374242276</v>
       </c>
       <c r="D12" t="n">
-        <v>26.81337402040266</v>
+        <v>4.357173278315432</v>
       </c>
       <c r="E12" t="n">
-        <v>7.98097201914586</v>
+        <v>1.296907953111202</v>
       </c>
       <c r="F12" t="n">
-        <v>7.986301554136606</v>
+        <v>1.297774002547199</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.36950287908994</v>
+        <v>4.122544217852115</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23009750897377</v>
+        <v>4.099890845208239</v>
       </c>
       <c r="E13" t="n">
-        <v>7.98097201914586</v>
+        <v>1.296907953111202</v>
       </c>
       <c r="F13" t="n">
-        <v>7.986301554136606</v>
+        <v>1.297774002547199</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>10.81083703654543</v>
+        <v>1.756761018438633</v>
       </c>
       <c r="D14" t="n">
-        <v>10.82440599030707</v>
+        <v>1.758965973424899</v>
       </c>
       <c r="E14" t="n">
-        <v>7.98097201914586</v>
+        <v>1.296907953111202</v>
       </c>
       <c r="F14" t="n">
-        <v>7.986301554136606</v>
+        <v>1.297774002547199</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>17.18109325405687</v>
+        <v>2.791927653784242</v>
       </c>
       <c r="D15" t="n">
-        <v>17.23549018735397</v>
+        <v>2.80076715544502</v>
       </c>
       <c r="E15" t="n">
-        <v>7.98097201914586</v>
+        <v>1.296907953111202</v>
       </c>
       <c r="F15" t="n">
-        <v>7.986301554136606</v>
+        <v>1.297774002547199</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>20.83683881553549</v>
+        <v>3.385986307524516</v>
       </c>
       <c r="D16" t="n">
-        <v>20.96437964088645</v>
+        <v>3.406711691644047</v>
       </c>
       <c r="E16" t="n">
-        <v>7.98097201914586</v>
+        <v>1.296907953111202</v>
       </c>
       <c r="F16" t="n">
-        <v>7.986301554136606</v>
+        <v>1.297774002547199</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>14.60913533893825</v>
+        <v>2.373984492577466</v>
       </c>
       <c r="D17" t="n">
-        <v>14.55736434258433</v>
+        <v>2.365571705669955</v>
       </c>
       <c r="E17" t="n">
-        <v>7.98097201914586</v>
+        <v>1.296907953111202</v>
       </c>
       <c r="F17" t="n">
-        <v>7.986301554136606</v>
+        <v>1.297774002547199</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>29.01986835108247</v>
+        <v>4.715728607050901</v>
       </c>
       <c r="D18" t="n">
-        <v>29.02008900115647</v>
+        <v>4.715764462687926</v>
       </c>
       <c r="E18" t="n">
-        <v>7.98097201914586</v>
+        <v>1.296907953111202</v>
       </c>
       <c r="F18" t="n">
-        <v>7.986301554136606</v>
+        <v>1.297774002547199</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>3.226264233230228</v>
+        <v>0.524267937899912</v>
       </c>
       <c r="D19" t="n">
-        <v>3.147637926202036</v>
+        <v>0.5114911630078308</v>
       </c>
       <c r="E19" t="n">
-        <v>7.98097201914586</v>
+        <v>1.296907953111202</v>
       </c>
       <c r="F19" t="n">
-        <v>7.986301554136606</v>
+        <v>1.297774002547199</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>8.215627679343157</v>
+        <v>1.335039497893263</v>
       </c>
       <c r="D20" t="n">
-        <v>8.225501711500121</v>
+        <v>1.33664402811877</v>
       </c>
       <c r="E20" t="n">
-        <v>7.98097201914586</v>
+        <v>1.296907953111202</v>
       </c>
       <c r="F20" t="n">
-        <v>7.986301554136606</v>
+        <v>1.297774002547199</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>22.10023987787238</v>
+        <v>3.591288980154262</v>
       </c>
       <c r="D21" t="n">
-        <v>22.06187870688071</v>
+        <v>3.585055289868115</v>
       </c>
       <c r="E21" t="n">
-        <v>7.98097201914586</v>
+        <v>1.296907953111202</v>
       </c>
       <c r="F21" t="n">
-        <v>7.986301554136606</v>
+        <v>1.297774002547199</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>19.86455435706129</v>
+        <v>3.227990083022461</v>
       </c>
       <c r="D22" t="n">
-        <v>19.7942353893812</v>
+        <v>3.216563250774445</v>
       </c>
       <c r="E22" t="n">
-        <v>7.98097201914586</v>
+        <v>1.296907953111202</v>
       </c>
       <c r="F22" t="n">
-        <v>7.986301554136606</v>
+        <v>1.297774002547199</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
